--- a/PMO领域全量Agent_Skill清单_v1.0.xlsx
+++ b/PMO领域全量Agent_Skill清单_v1.0.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,8 +36,17 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00006100"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -50,8 +59,23 @@
         <bgColor rgb="002F5496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -65,11 +89,14 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -78,6 +105,14 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,14 +481,14 @@
   <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -664,20 +699,26 @@
   <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="42" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="29" customWidth="1" min="11" max="11"/>
+    <col width="38" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="19" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -835,7 +876,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -914,7 +955,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -993,7 +1034,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -1072,7 +1113,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -1151,7 +1192,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -1230,7 +1271,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -1309,7 +1350,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -1388,7 +1429,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -1471,7 +1512,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -1550,7 +1591,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -1633,7 +1674,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -1712,7 +1753,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P13" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -1791,7 +1832,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P14" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -1870,7 +1911,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P15" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -1949,7 +1990,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P16" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -2028,7 +2069,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P17" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -2107,7 +2148,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P18" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -2186,7 +2227,7 @@
           <t>C</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P19" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -2269,7 +2310,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P20" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -2348,7 +2389,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P21" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -2427,7 +2468,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P22" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -2506,7 +2547,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P23" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -2589,7 +2630,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P24" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -2668,7 +2709,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P25" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -2747,7 +2788,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P26" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -2826,7 +2867,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P27" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -2905,7 +2946,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P28" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -2984,7 +3025,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P29" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -3063,7 +3104,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P30" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -3142,7 +3183,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P31" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -3225,7 +3266,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="P32" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -3304,7 +3345,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P33" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -3383,7 +3424,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="P34" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -3462,7 +3503,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="P35" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -3541,7 +3582,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P36" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -3624,7 +3665,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="P37" s="5" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
@@ -3693,9 +3734,19 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>已废弃，由scope-management替代</t>
+      <c r="N38" s="7" t="inlineStr">
+        <is>
+          <t>Deprecated（已废弃隔离）</t>
+        </is>
+      </c>
+      <c r="P38" s="5" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -3757,9 +3808,19 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>已废弃，由scope-management替代</t>
+      <c r="N39" s="7" t="inlineStr">
+        <is>
+          <t>Deprecated（已废弃隔离）</t>
+        </is>
+      </c>
+      <c r="P39" s="5" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
